--- a/trade-operations-reconciliation-project.xlsx
+++ b/trade-operations-reconciliation-project.xlsx
@@ -2,72 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANIKETH\Desktop\CFI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANIKETH\Desktop\CFI\Project1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFE3986-2478-4D60-BBCF-4A9EFEDA05D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838CDACB-B8C9-4763-AA35-5EDF8D6F28A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{456BAC6A-C5B0-4C02-A2D4-FCA88585F7A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{456BAC6A-C5B0-4C02-A2D4-FCA88585F7A2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Dashboards" sheetId="5" r:id="rId1"/>
     <sheet name="Readme Summary" sheetId="9" r:id="rId2"/>
-    <sheet name="Dashboard" sheetId="6" r:id="rId3"/>
-    <sheet name="Internal Trade Data" sheetId="1" r:id="rId4"/>
-    <sheet name="Broker Trade Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Reconciliation" sheetId="3" r:id="rId6"/>
-    <sheet name="Break Report" sheetId="4" r:id="rId7"/>
+    <sheet name="Internal Trade Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Broker Trade Data" sheetId="2" r:id="rId4"/>
+    <sheet name="Reconciliation" sheetId="3" r:id="rId5"/>
+    <sheet name="Break Report" sheetId="4" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Project1.xlsxTable2AssetType1" hidden="1">Table2[Asset Type]</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
-      <x15:dataModel>
-        <x15:modelTables>
-          <x15:modelTable id="Table2 Asset Type" name="Table2 Asset Type" connection="WorksheetConnection_Project1.xlsx!Table2[Asset Type]"/>
-        </x15:modelTables>
-      </x15:dataModel>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{8F51384E-2364-4D8A-A27C-023AC094C8C3}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
-    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
-    <olapPr sendLocale="1" rowDrillCount="1000"/>
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="2" xr16:uid="{E009D779-D47A-4103-9EC5-66CFC10493C4}" name="WorksheetConnection_Project1.xlsx!Table2[Asset Type]" type="102" refreshedVersion="8" minRefreshableVersion="5">
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="Table2 Asset Type" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Project1.xlsxTable2AssetType1"/>
-        </x15:connection>
-      </ext>
-    </extLst>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="120">
   <si>
     <t>Trade ID</t>
   </si>
@@ -393,13 +356,140 @@
     <t>Break %</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
     <t>Trade Operations Reconciliation &amp; Break Analysis</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>% of Total Trades</t>
+  </si>
+  <si>
+    <t>Trade Reconciliation &amp; Break Analysis Dashboard</t>
+  </si>
+  <si>
+    <t>Post-Trade Operations Monitoring</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">31
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total Trades</t>
+    </r>
+  </si>
+  <si>
+    <t>Trades</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total Breaks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16%</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Break Rate</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Asset Classes</t>
+    </r>
+  </si>
+  <si>
+    <t>Built in Excel | Trade Operations Simulation Project</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF163763"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Operational Insights</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Equity trades represented the highest trading activity
+• Quantity and price mismatches were the most common breaks
+• Overall reconciliation break rate remained at 16%
+• Missing trades highlighted settlement monitoring exceptions</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -409,7 +499,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,8 +529,77 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.749992370372631"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF163763"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,8 +612,26 @@
         <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF163763"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -488,13 +665,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -512,13 +769,71 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -526,7 +841,12 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -534,26 +854,32 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -585,23 +911,50 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -682,6 +1035,24 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="thin">
           <color theme="1"/>
@@ -721,6 +1092,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF163763"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -766,17 +1142,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1"/>
+              <a:rPr lang="en-IN" sz="1600"/>
               <a:t>Asset</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1600"/>
-              <a:t> </a:t>
+              <a:rPr lang="en-IN" sz="1600" baseline="0"/>
+              <a:t> Type Distribuiton</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1"/>
-              <a:t>Types</a:t>
-            </a:r>
+            <a:endParaRPr lang="en-IN" sz="1600"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -810,146 +1183,6 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -960,11 +1193,19 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Total</c:v>
+            <c:strRef>
+              <c:f>Dashboards!$C$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Trades</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="163763"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1031,43 +1272,49 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strLit>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>Derivative</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>Equity</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>ETF</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Fixed Income</c:v>
-              </c:pt>
-            </c:strLit>
+            <c:strRef>
+              <c:f>Dashboards!$B$42:$B$45</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Equity</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ETF</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Fixed Income</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Derivative</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
-              <c:pt idx="0">
-                <c:v>4</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>15</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>6</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>6</c:v>
-              </c:pt>
-            </c:numLit>
+            <c:numRef>
+              <c:f>Dashboards!$C$42:$C$45</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1512-4F20-B8A3-565CB0E1953A}"/>
+              <c16:uniqueId val="{00000000-7B11-44B1-B2F6-E3CB0275217C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1082,29 +1329,24 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1022444495"/>
-        <c:axId val="1022458895"/>
+        <c:axId val="1173177472"/>
+        <c:axId val="1173177952"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1022444495"/>
+        <c:axId val="1173177472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:round/>
           </a:ln>
           <a:effectLst/>
@@ -1129,7 +1371,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1022458895"/>
+        <c:crossAx val="1173177952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1137,28 +1379,14 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1022458895"/>
+        <c:axId val="1173177952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1188,7 +1416,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1022444495"/>
+        <c:crossAx val="1173177472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1203,44 +1431,13 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="accent3">
-            <a:lumMod val="0"/>
-            <a:lumOff val="100000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="10000">
-          <a:schemeClr val="bg1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="accent3">
-            <a:lumMod val="100000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1260,11 +1457,347 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst/>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1600"/>
+              <a:t>Break Type Analysis</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboards!$F$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboards!$E$42:$E$44</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Quantity Breaks</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Price Breaks</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Missing Trades</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboards!$F$42:$F$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0513-4244-BD5B-95C90655E49B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1061988832"/>
+        <c:axId val="1061988352"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1061988832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1061988352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1061988352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1061988832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1285,11 +1818,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1299,19 +1832,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Break Distribution</a:t>
+              <a:t>Break Type Distribuition Percentages</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.31657633420822395"/>
-          <c:y val="3.2407407407407406E-2"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1325,11 +1850,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1347,15 +1872,15 @@
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Break Report'!$B$37</c:f>
+              <c:f>'Break Report'!$F$37</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Value</c:v>
+                  <c:v>% of Total Trades</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1367,22 +1892,13 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
+              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-74A0-4794-BC16-CE947FCCFDBC}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1391,22 +1907,13 @@
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
               </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
+              <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-74A0-4794-BC16-CE947FCCFDBC}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1415,49 +1922,21 @@
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-74A0-4794-BC16-CE947FCCFDBC}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:pattFill prst="pct75">
-                <a:fgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:fgClr>
-                <a:bgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:bgClr>
-              </a:pattFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
+              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -1466,9 +1945,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1478,23 +1960,24 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="ctr"/>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
+            <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="9525">
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
                     </a:schemeClr>
                   </a:solidFill>
+                  <a:round/>
                 </a:ln>
                 <a:effectLst/>
               </c:spPr>
@@ -1505,14 +1988,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Break Report'!$A$38:$A$43</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Break Report'!$A$40:$A$42</c:f>
+              <c:f>'Break Report'!$D$38:$D$40</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1529,54 +2005,219 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Break Report'!$B$38:$B$43</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Break Report'!$B$40:$B$42</c:f>
+              <c:f>'Break Report'!$F$38:$F$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>9.7000000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>9.7000000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>3.2000000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:categoryFilterExceptions>
-                <c15:categoryFilterException>
-                  <c15:sqref>'Break Report'!$B$38</c15:sqref>
-                  <c15:explosion val="15"/>
-                </c15:categoryFilterException>
-              </c15:categoryFilterExceptions>
-            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-74A0-4794-BC16-CE947FCCFDBC}"/>
+              <c16:uniqueId val="{00000001-104E-4312-8F05-A0BD6AAF369D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="ctr"/>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Break Report'!$E$37</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Count</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="19050">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="1"/>
+                  <c:leaderLines>
+                    <c:spPr>
+                      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="35000"/>
+                            <a:lumOff val="65000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:round/>
+                      </a:ln>
+                      <a:effectLst/>
+                    </c:spPr>
+                  </c:leaderLines>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Break Report'!$D$38:$D$40</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>Quantity Breaks</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Price Breaks</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Missing Trades</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Break Report'!$E$38:$E$40</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-104E-4312-8F05-A0BD6AAF369D}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
       </c:pieChart>
       <c:spPr>
         <a:noFill/>
@@ -1587,25 +2228,10 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.69346719160104997"/>
-          <c:y val="0.3758092738407699"/>
-          <c:w val="0.20653280839895011"/>
-          <c:h val="0.23437664041994752"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1618,9 +2244,9 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1644,30 +2270,14 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -1733,6 +2343,12 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2276,238 +2892,171 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
             <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2523,19 +3072,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2545,22 +3096,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2569,17 +3121,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2588,12 +3140,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -2607,36 +3159,30 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -2646,28 +3192,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2676,17 +3211,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2695,16 +3230,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2713,35 +3249,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -2749,22 +3277,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2772,14 +3289,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2791,12 +3308,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2805,13 +3322,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2820,9 +3338,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2832,19 +3350,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2853,16 +3372,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2870,13 +3384,676 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>853441</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>192158</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8C10A5A-0AB7-0F1C-7015-CE8A995DA18C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>284922</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52136</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>60959</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFEE695D-018E-2AFF-263E-03E8A7647808}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7BF7A79-8A4F-FA0B-1ED2-B2A5A1064065}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="15240"/>
+          <a:ext cx="7604760" cy="5516880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3628,7 +4805,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Role?Focus: Trade Operations/Capital Markets.</a:t>
+            <a:t>Role/Focus: Trade Operations/Capital Markets.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3638,27 +4815,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>201930</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E67084BE-D0C0-9FBF-B0B9-A9E8DF191FCB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BBD97A0-A432-076D-D831-E66CEB5AEB99}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3676,155 +4853,38 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DA0E34-559C-41AE-9367-817C342B94D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="ANIKETH" refreshedDate="46141.585274189812" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5E9BCC6F-882F-4BDB-B3D8-4CF35CEDF502}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="1">
-    <cacheField name="[Table2 Asset Type].[Asset Type].[Asset Type]" caption="Asset Type" numFmtId="0" level="1">
-      <sharedItems count="4">
-        <s v="Derivative"/>
-        <s v="Equity"/>
-        <s v="ETF"/>
-        <s v="Fixed Income"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="3">
-    <cacheHierarchy uniqueName="[Table2 Asset Type].[Asset Type]" caption="Asset Type" attribute="1" defaultMemberUniqueName="[Table2 Asset Type].[Asset Type].[All]" allUniqueName="[Table2 Asset Type].[Asset Type].[All]" dimensionUniqueName="[Table2 Asset Type]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table2 Asset Type]" caption="__XL_Count Table2 Asset Type" measure="1" displayFolder="" measureGroup="Table2 Asset Type" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table2 Asset Type" uniqueName="[Table2 Asset Type]" caption="Table2 Asset Type"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table2 Asset Type" caption="Table2 Asset Type"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7158AA1E-335F-46C7-A3D7-51F6D8D684E0}" name="Table6" displayName="Table6" ref="B41:C45" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="B41:C45" xr:uid="{7158AA1E-335F-46C7-A3D7-51F6D8D684E0}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{059C2E83-BA41-4BC0-94FD-13F2D903B3E6}" name="Asset Type" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{51A00A81-FC8D-45DD-AEF3-52005C6049EA}" name="Trades" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D1AD38A-583E-4BCA-9D34-15364ABB43BC}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="1">
-    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <pivotHierarchies count="3">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="0"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Project1.xlsx!Table2[Asset Type]">
-        <x15:activeTabTopLevelEntity name="[Table2 Asset Type]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{EF643DEE-1DC8-4E27-8173-2B0D6E3D4594}" name="Table7" displayName="Table7" ref="E41:F44" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="E41:F44" xr:uid="{EF643DEE-1DC8-4E27-8173-2B0D6E3D4594}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{26D4F2C6-7369-44B4-BACD-4C4B0C8543E9}" name="Break Type" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C8ED01DA-5CCE-47BC-B647-6F288E1A5212}" name="Count" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05832583-3EED-4B45-BFBD-4CB1B6D3052C}" name="Table2" displayName="Table2" ref="A1:K32" totalsRowShown="0">
   <autoFilter ref="A1:K32" xr:uid="{05832583-3EED-4B45-BFBD-4CB1B6D3052C}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{D55E3BAB-BE84-4FEB-A496-64EBCC155DBA}" name="Trade ID"/>
-    <tableColumn id="2" xr3:uid="{CA1761B7-23C8-49C4-B518-7674FF2D7B02}" name="Trade Date" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{A72B0373-D12A-4373-9AE5-7B0C72FCDD1B}" name="Settlement Date" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{CA1761B7-23C8-49C4-B518-7674FF2D7B02}" name="Trade Date" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{A72B0373-D12A-4373-9AE5-7B0C72FCDD1B}" name="Settlement Date" dataDxfId="32"/>
     <tableColumn id="4" xr3:uid="{746A13EF-976F-4A9E-8FAC-D0AF5AB79075}" name="Asset Type"/>
     <tableColumn id="5" xr3:uid="{3174925B-EBCA-4713-B110-E1062B52A5C3}" name="Security Name"/>
     <tableColumn id="6" xr3:uid="{A489DCC0-A224-42B7-B666-DAB5336EF0B9}" name="Buy/Sell"/>
@@ -3838,13 +4898,13 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{44917C04-C0CD-4C96-8137-D6F6BF47AB7E}" name="Table3" displayName="Table3" ref="A1:K32" totalsRowShown="0">
   <autoFilter ref="A1:K32" xr:uid="{44917C04-C0CD-4C96-8137-D6F6BF47AB7E}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{DF591813-793F-448D-9A08-7EA3326A3430}" name="Trade ID"/>
-    <tableColumn id="2" xr3:uid="{FFD1B513-1D96-4DC0-894A-4EF3D659DBBC}" name="Trade Date" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{3D855ABD-93B7-48D1-A285-04CC64C3677D}" name="Settlement Date" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{FFD1B513-1D96-4DC0-894A-4EF3D659DBBC}" name="Trade Date" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{3D855ABD-93B7-48D1-A285-04CC64C3677D}" name="Settlement Date" dataDxfId="30"/>
     <tableColumn id="4" xr3:uid="{4E01239A-ED2F-4E35-BF96-EBF7B4B71C51}" name="Asset Type"/>
     <tableColumn id="5" xr3:uid="{811D2141-D08B-43E5-B5D2-0DF0E33C489C}" name="Security Name"/>
     <tableColumn id="6" xr3:uid="{06203CCE-727F-4EA5-930C-3CA26A55584A}" name="Buy/Sell"/>
@@ -3858,36 +4918,36 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4162D666-A2B2-42C4-94BC-3748B73D6E17}" name="Table4" displayName="Table4" ref="A1:I32" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="20">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4162D666-A2B2-42C4-94BC-3748B73D6E17}" name="Table4" displayName="Table4" ref="A1:I32" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28">
   <autoFilter ref="A1:I32" xr:uid="{4162D666-A2B2-42C4-94BC-3748B73D6E17}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I32">
-    <sortCondition sortBy="fontColor" ref="I2:I32" dxfId="2"/>
+    <sortCondition sortBy="fontColor" ref="I2:I32" dxfId="27"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C824A3AC-C0EB-4746-B6C7-DD6EB6E91EA5}" name="Trade ID" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{C824A3AC-C0EB-4746-B6C7-DD6EB6E91EA5}" name="Trade ID" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{14AFCAD2-E9B5-45A8-8797-C505488DDB58}" name="Internal Qty">
       <calculatedColumnFormula>VLOOKUP(A2,Table2[#All],7,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3664AA68-9A0C-4CF8-8541-C4DE788889CE}" name="Broker Qty" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{3664AA68-9A0C-4CF8-8541-C4DE788889CE}" name="Broker Qty" dataDxfId="25">
       <calculatedColumnFormula>IFERROR(VLOOKUP(A2,Table3[#All],7,FALSE),"Missing")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{66F27D82-9751-4A48-861E-44ED90FAB46C}" name="Qty Match" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{66F27D82-9751-4A48-861E-44ED90FAB46C}" name="Qty Match" dataDxfId="24">
       <calculatedColumnFormula>IF(Table4[[#This Row],[Broker Qty]]="Missing","Missing",IF(Table4[[#This Row],[Internal Qty]]=Table4[[#This Row],[Broker Qty]],"Match","Break"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0F0EF7B6-1DF4-4AE5-9CB0-F40DDEC23D6C}" name="Internal Price">
       <calculatedColumnFormula>VLOOKUP(A2,Table2[#All],8,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DF049F08-D0E7-44E8-BCEC-51BBE201F0A3}" name="Broker Price" dataDxfId="16">
+    <tableColumn id="6" xr3:uid="{DF049F08-D0E7-44E8-BCEC-51BBE201F0A3}" name="Broker Price" dataDxfId="23">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Table4[[#This Row],[Trade ID]],Table3[#All],8,FALSE),"Missing")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{19FD193F-24C8-458F-8106-DBFFAB6EBEC3}" name="Price Match" dataDxfId="15">
+    <tableColumn id="7" xr3:uid="{19FD193F-24C8-458F-8106-DBFFAB6EBEC3}" name="Price Match" dataDxfId="22">
       <calculatedColumnFormula>IF(Table4[[#This Row],[Internal Price]]=Table4[[#This Row],[Broker Price]],"Match","Break")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{28550DAD-CEFF-40D3-AAF8-5C452E10955D}" name="Broker Status" dataDxfId="14">
+    <tableColumn id="8" xr3:uid="{28550DAD-CEFF-40D3-AAF8-5C452E10955D}" name="Broker Status" dataDxfId="21">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Table4[[#This Row],[Trade ID]],Table3[#All],11,FALSE),"Missing")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{81F1DA02-7DD6-4882-AA02-A6DA05B7A8C7}" name="Break Type" dataDxfId="13">
+    <tableColumn id="9" xr3:uid="{81F1DA02-7DD6-4882-AA02-A6DA05B7A8C7}" name="Break Type" dataDxfId="20">
       <calculatedColumnFormula>IF(Table4[[#This Row],[Broker Qty]]="Missing","Missing Trade",IF(Table4[[#This Row],[Qty Match]]="Break","Quantity Break",IF(Table4[[#This Row],[Price Match]]="Break","Price Break","No Break")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3895,8 +4955,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D1E6DEE1-7511-4C47-B781-A7CF1D669A20}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="12">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D1E6DEE1-7511-4C47-B781-A7CF1D669A20}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="19">
   <autoFilter ref="A1:E31" xr:uid="{D1E6DEE1-7511-4C47-B781-A7CF1D669A20}">
     <filterColumn colId="0">
       <customFilters>
@@ -3911,13 +4971,13 @@
     <tableColumn id="2" xr3:uid="{02D0D294-6E3D-4C3E-B984-10E0B9240042}" name="Break Type">
       <calculatedColumnFormula>IF(Table4[[#This Row],[Break Type]]&lt;&gt;"No Break",Table4[[#This Row],[Break Type]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0F6B5D65-0EFD-4BC1-854B-0C9C8015617E}" name="Root Cause" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{0F6B5D65-0EFD-4BC1-854B-0C9C8015617E}" name="Root Cause" dataDxfId="18">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Break Type]]="Quantity Break","Quantity mismatch between Internal Trade and Broker",IF(Table1[[#This Row],[Break Type]]="Price Break","Price mismatch between Internal Trade and Broker",IF(Table1[[#This Row],[Break Type]]="Missing Trade","Trade missing in broker data","")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DA07A570-75D1-4B1D-AF61-F9823B06454B}" name="Action Required" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{DA07A570-75D1-4B1D-AF61-F9823B06454B}" name="Action Required" dataDxfId="17">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Break Type]]="Quantity Break","Confirm quantity with broker",IF(Table1[[#This Row],[Break Type]]="Price Break","Check price with brocker",IF(Table1[[#This Row],[Break Type]]="Missing Trade","contact broker to confirm Trade","")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{068CA2E3-585E-4CD0-BD07-167A647E16DC}" name="Status" dataDxfId="9">
+    <tableColumn id="5" xr3:uid="{068CA2E3-585E-4CD0-BD07-167A647E16DC}" name="Status" dataDxfId="16">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Trade ID]]="","","Open")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3925,12 +4985,12 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F6E68571-D8F2-4910-AF50-F46698755906}" name="Table5" displayName="Table5" ref="A37:B43" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F6E68571-D8F2-4910-AF50-F46698755906}" name="Table5" displayName="Table5" ref="A37:B43" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A37:B43" xr:uid="{F6E68571-D8F2-4910-AF50-F46698755906}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{47C1C04A-E2B7-4FF0-AAAB-DC8D0F799645}" name="Metric" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{1BF2C010-6D43-496A-A378-B73D52AE5534}" name="Value" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{47C1C04A-E2B7-4FF0-AAAB-DC8D0F799645}" name="Metric" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1BF2C010-6D43-496A-A378-B73D52AE5534}" name="Value" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4233,44 +5293,273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50AC78C-F235-4C70-8F1A-DCDB249CCA0B}">
-  <dimension ref="A3:A8"/>
+  <dimension ref="A3:L45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="12" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="12"/>
+    <col min="5" max="5" width="12.21875" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="32"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+    </row>
+    <row r="8" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="E8" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="H8" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I8" s="17"/>
+      <c r="K8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="26"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="26"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="26"/>
+    </row>
+    <row r="29" spans="2:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="27"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="29"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+    </row>
+    <row r="41" spans="2:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="7">
+        <v>15</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="7">
+        <v>6</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="7">
+        <v>6</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>109</v>
+      <c r="C45" s="7">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B25:L29"/>
+    <mergeCell ref="H32:L32"/>
+    <mergeCell ref="A3:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="E8:F10"/>
+    <mergeCell ref="H8:I10"/>
+    <mergeCell ref="K8:L10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -4283,159 +5572,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>110</v>
+      <c r="A1" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
+      <c r="A2" s="10"/>
     </row>
     <row r="3" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
+      <c r="A3" s="10"/>
     </row>
     <row r="4" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
+      <c r="A4" s="10"/>
     </row>
     <row r="5" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="A5" s="10"/>
     </row>
     <row r="6" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
+      <c r="A6" s="10"/>
     </row>
     <row r="7" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
+      <c r="A7" s="10"/>
     </row>
     <row r="8" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
+      <c r="A8" s="10"/>
     </row>
     <row r="9" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
+      <c r="A9" s="10"/>
     </row>
     <row r="10" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
+      <c r="A10" s="10"/>
     </row>
     <row r="11" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
+      <c r="A11" s="10"/>
     </row>
     <row r="12" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+      <c r="A12" s="10"/>
     </row>
     <row r="13" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="A13" s="10"/>
     </row>
     <row r="14" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
+      <c r="A14" s="10"/>
     </row>
     <row r="15" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
+      <c r="A15" s="10"/>
     </row>
     <row r="16" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
+      <c r="A16" s="10"/>
     </row>
     <row r="17" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="A17" s="10"/>
     </row>
     <row r="18" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
+      <c r="A18" s="10"/>
     </row>
     <row r="19" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
+      <c r="A19" s="10"/>
     </row>
     <row r="20" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
+      <c r="A20" s="10"/>
     </row>
     <row r="21" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
+      <c r="A21" s="10"/>
     </row>
     <row r="22" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
+      <c r="A22" s="10"/>
     </row>
     <row r="23" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
+      <c r="A23" s="10"/>
     </row>
     <row r="24" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
+      <c r="A24" s="10"/>
     </row>
     <row r="25" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
+      <c r="A25" s="10"/>
     </row>
     <row r="26" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
+      <c r="A26" s="10"/>
     </row>
     <row r="27" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
+      <c r="A27" s="10"/>
     </row>
     <row r="28" spans="1:1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
+      <c r="A28" s="10"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
+      <c r="A29" s="10"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
+      <c r="A30" s="10"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
+      <c r="A31" s="10"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
+      <c r="A32" s="10"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
+      <c r="A33" s="10"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
+      <c r="A34" s="10"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
+      <c r="A35" s="10"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
+      <c r="A36" s="10"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
+      <c r="A37" s="10"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
+      <c r="A38" s="10"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
+      <c r="A39" s="10"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
+      <c r="A40" s="10"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
+      <c r="A41" s="10"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
+      <c r="A42" s="10"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
+      <c r="A43" s="10"/>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
+      <c r="A44" s="10"/>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
+      <c r="A45" s="10"/>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
+      <c r="A46" s="10"/>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
+      <c r="A47" s="10"/>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
+      <c r="A48" s="10"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
+      <c r="A49" s="10"/>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
+      <c r="A50" s="10"/>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
+      <c r="A51" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4447,24 +5736,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD38461-99F9-4522-912D-4A0341DA2EEA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3543DDC5-B94D-492D-A42F-D53FA4EE9D88}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4477,7 +5748,7 @@
     <col min="6" max="6" width="9.88671875" customWidth="1"/>
     <col min="7" max="7" width="10.21875" customWidth="1"/>
     <col min="8" max="8" width="9.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="9" customWidth="1"/>
     <col min="10" max="10" width="14.109375" customWidth="1"/>
     <col min="11" max="11" width="8.109375" customWidth="1"/>
   </cols>
@@ -4507,7 +5778,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -4542,7 +5813,7 @@
       <c r="H2">
         <v>190</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>19000</v>
       </c>
       <c r="J2" t="s">
@@ -4577,7 +5848,7 @@
       <c r="H3">
         <v>410</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <v>30750</v>
       </c>
       <c r="J3" t="s">
@@ -4612,7 +5883,7 @@
       <c r="H4">
         <v>175</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <v>8750</v>
       </c>
       <c r="J4" t="s">
@@ -4647,7 +5918,7 @@
       <c r="H5">
         <v>515</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="9">
         <v>61800</v>
       </c>
       <c r="J5" t="s">
@@ -4682,7 +5953,7 @@
       <c r="H6">
         <v>42.5</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>Table2[[#This Row],[Quantity]]*Table2[[#This Row],[Price]]</f>
         <v>42500</v>
       </c>
@@ -4718,7 +5989,7 @@
       <c r="H7">
         <v>98.5</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <v>19700</v>
       </c>
       <c r="J7" t="s">
@@ -4753,7 +6024,7 @@
       <c r="H8">
         <v>185</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <v>11100</v>
       </c>
       <c r="J8" t="s">
@@ -4788,7 +6059,7 @@
       <c r="H9">
         <v>5250</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>52500</v>
       </c>
       <c r="J9" t="s">
@@ -4823,7 +6094,7 @@
       <c r="H10">
         <v>880</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>35200</v>
       </c>
       <c r="J10" t="s">
@@ -4858,7 +6129,7 @@
       <c r="H11">
         <v>440</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <v>39600</v>
       </c>
       <c r="J11" t="s">
@@ -4893,7 +6164,7 @@
       <c r="H12">
         <v>101.2</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <v>15180</v>
       </c>
       <c r="J12" t="s">
@@ -4928,7 +6199,7 @@
       <c r="H13">
         <v>485</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>26675</v>
       </c>
       <c r="J13" t="s">
@@ -4963,7 +6234,7 @@
       <c r="H14">
         <v>610</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>18300</v>
       </c>
       <c r="J14" t="s">
@@ -4998,7 +6269,7 @@
       <c r="H15">
         <v>205</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <v>20500</v>
       </c>
       <c r="J15" t="s">
@@ -5033,7 +6304,7 @@
       <c r="H16">
         <v>99.8</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <v>24950</v>
       </c>
       <c r="J16" t="s">
@@ -5068,7 +6339,7 @@
       <c r="H17">
         <v>82</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="9">
         <v>1230</v>
       </c>
       <c r="J17" t="s">
@@ -5103,7 +6374,7 @@
       <c r="H18">
         <v>198</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <v>15840</v>
       </c>
       <c r="J18" t="s">
@@ -5138,7 +6409,7 @@
       <c r="H19">
         <v>38</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="9">
         <v>7600</v>
       </c>
       <c r="J19" t="s">
@@ -5173,7 +6444,7 @@
       <c r="H20">
         <v>255</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="9">
         <v>17850</v>
       </c>
       <c r="J20" t="s">
@@ -5208,7 +6479,7 @@
       <c r="H21">
         <v>99.1</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="9">
         <v>29730</v>
       </c>
       <c r="J21" t="s">
@@ -5243,7 +6514,7 @@
       <c r="H22">
         <v>160</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <v>7200</v>
       </c>
       <c r="J22" t="s">
@@ -5278,7 +6549,7 @@
       <c r="H23">
         <v>18200</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="9">
         <v>145600</v>
       </c>
       <c r="J23" t="s">
@@ -5313,7 +6584,7 @@
       <c r="H24">
         <v>275</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="9">
         <v>17875</v>
       </c>
       <c r="J24" t="s">
@@ -5348,7 +6619,7 @@
       <c r="H25">
         <v>78</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="9">
         <v>8580</v>
       </c>
       <c r="J25" t="s">
@@ -5383,7 +6654,7 @@
       <c r="H26">
         <v>102.4</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="9">
         <v>18432</v>
       </c>
       <c r="J26" t="s">
@@ -5418,7 +6689,7 @@
       <c r="H27">
         <v>285</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="9">
         <v>9975</v>
       </c>
       <c r="J27" t="s">
@@ -5453,7 +6724,7 @@
       <c r="H28">
         <v>470</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="9">
         <v>11750</v>
       </c>
       <c r="J28" t="s">
@@ -5488,7 +6759,7 @@
       <c r="H29">
         <v>2350</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="9">
         <v>28200</v>
       </c>
       <c r="J29" t="s">
@@ -5523,7 +6794,7 @@
       <c r="H30">
         <v>48</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="9">
         <v>4560</v>
       </c>
       <c r="J30" t="s">
@@ -5558,7 +6829,7 @@
       <c r="H31">
         <v>76</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <v>9880</v>
       </c>
       <c r="J31" t="s">
@@ -5593,7 +6864,7 @@
       <c r="H32">
         <v>525</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="9">
         <v>14700</v>
       </c>
       <c r="J32" t="s">
@@ -5605,7 +6876,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:K1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5614,7 +6885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7455377A-22F3-494C-B75E-C1F431485E43}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5626,7 +6897,7 @@
     <col min="5" max="5" width="15.109375" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" customWidth="1"/>
     <col min="7" max="7" width="10.21875" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="9" customWidth="1"/>
     <col min="10" max="10" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5655,7 +6926,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -5690,7 +6961,7 @@
       <c r="H2">
         <v>190</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>19000</v>
       </c>
       <c r="J2" t="s">
@@ -5725,7 +6996,7 @@
       <c r="H3">
         <v>410</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <v>30750</v>
       </c>
       <c r="J3" t="s">
@@ -5760,7 +7031,7 @@
       <c r="H4">
         <v>175</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <v>8750</v>
       </c>
       <c r="J4" t="s">
@@ -5795,7 +7066,7 @@
       <c r="H5">
         <v>515</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="9">
         <v>61800</v>
       </c>
       <c r="J5" t="s">
@@ -5830,7 +7101,7 @@
       <c r="H6">
         <v>42.5</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>Table3[[#This Row],[Quantity]]*Table3[[#This Row],[Price]]</f>
         <v>425000</v>
       </c>
@@ -5866,7 +7137,7 @@
       <c r="H7">
         <v>98.5</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <v>21670</v>
       </c>
       <c r="J7" t="s">
@@ -5901,7 +7172,7 @@
       <c r="H8">
         <v>185</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <v>11100</v>
       </c>
       <c r="J8" t="s">
@@ -5936,7 +7207,7 @@
       <c r="H9">
         <v>5250</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>52500</v>
       </c>
       <c r="J9" t="s">
@@ -5971,7 +7242,7 @@
       <c r="H10">
         <v>880</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>35200</v>
       </c>
       <c r="J10" t="s">
@@ -6006,7 +7277,7 @@
       <c r="H11">
         <v>442</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <v>39780</v>
       </c>
       <c r="J11" t="s">
@@ -6041,7 +7312,7 @@
       <c r="H12">
         <v>101.2</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <v>15180</v>
       </c>
       <c r="J12" t="s">
@@ -6076,7 +7347,7 @@
       <c r="H13">
         <v>485</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>26675</v>
       </c>
       <c r="J13" t="s">
@@ -6111,7 +7382,7 @@
       <c r="H14">
         <v>610</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>18300</v>
       </c>
       <c r="J14" t="s">
@@ -6146,7 +7417,7 @@
       <c r="H15">
         <v>205</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <v>20500</v>
       </c>
       <c r="J15" t="s">
@@ -6181,7 +7452,7 @@
       <c r="H16">
         <v>82</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <v>1230</v>
       </c>
       <c r="J16" t="s">
@@ -6216,7 +7487,7 @@
       <c r="H17">
         <v>198</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="9">
         <v>15840</v>
       </c>
       <c r="J17" t="s">
@@ -6251,7 +7522,7 @@
       <c r="H18">
         <v>38</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <v>7600</v>
       </c>
       <c r="J18" t="s">
@@ -6286,7 +7557,7 @@
       <c r="H19">
         <v>255</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="9">
         <v>17850</v>
       </c>
       <c r="J19" t="s">
@@ -6321,7 +7592,7 @@
       <c r="H20">
         <v>99.1</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="9">
         <v>29730</v>
       </c>
       <c r="J20" t="s">
@@ -6356,7 +7627,7 @@
       <c r="H21">
         <v>160</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="9">
         <v>7200</v>
       </c>
       <c r="J21" t="s">
@@ -6391,7 +7662,7 @@
       <c r="H22">
         <v>18200</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <v>145600</v>
       </c>
       <c r="J22" t="s">
@@ -6426,7 +7697,7 @@
       <c r="H23">
         <v>275</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="9">
         <v>17875</v>
       </c>
       <c r="J23" t="s">
@@ -6461,7 +7732,7 @@
       <c r="H24">
         <v>78</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="9">
         <v>8580</v>
       </c>
       <c r="J24" t="s">
@@ -6496,7 +7767,7 @@
       <c r="H25">
         <v>102.4</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="9">
         <v>18432</v>
       </c>
       <c r="J25" t="s">
@@ -6531,7 +7802,7 @@
       <c r="H26">
         <v>285</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="9">
         <v>9975</v>
       </c>
       <c r="J26" t="s">
@@ -6566,7 +7837,7 @@
       <c r="H27">
         <v>470</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="9">
         <v>11750</v>
       </c>
       <c r="J27" t="s">
@@ -6601,7 +7872,7 @@
       <c r="H28">
         <v>2360</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="9">
         <v>28320</v>
       </c>
       <c r="J28" t="s">
@@ -6636,7 +7907,7 @@
       <c r="H29">
         <v>48</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="9">
         <v>4560</v>
       </c>
       <c r="J29" t="s">
@@ -6671,7 +7942,7 @@
       <c r="H30">
         <v>76</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="9">
         <v>9880</v>
       </c>
       <c r="J30" t="s">
@@ -6706,7 +7977,7 @@
       <c r="H31">
         <v>525</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <v>14700</v>
       </c>
       <c r="J31" t="s">
@@ -6741,7 +8012,7 @@
       <c r="H32">
         <v>68</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="9">
         <v>6800</v>
       </c>
       <c r="J32" t="s">
@@ -6759,20 +8030,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B55D5C1-35B4-4F84-AD20-E15A913AC186}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7953,14 +9224,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Break">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Match">
+      <formula>NOT(ISERROR(SEARCH("Match",G1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Break">
       <formula>NOT(ISERROR(SEARCH("Break",G1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Match">
-      <formula>NOT(ISERROR(SEARCH("Match",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7970,9 +9241,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3DB3FC-F159-446B-AAE9-F521B4F21A92}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -8658,15 +9929,24 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>102</v>
       </c>
@@ -8674,8 +9954,17 @@
         <f>COUNTA(Table4[Trade ID])</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D38" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3</v>
+      </c>
+      <c r="F38" s="11">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>103</v>
       </c>
@@ -8683,8 +9972,17 @@
         <f>COUNTIF(Table4[],"Break")</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D39" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3</v>
+      </c>
+      <c r="F39" s="11">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>104</v>
       </c>
@@ -8692,8 +9990,17 @@
         <f>COUNTIF(Table4[Qty Match],"&lt;&gt;Match")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D40" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>105</v>
       </c>
@@ -8702,7 +10009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>106</v>
       </c>
@@ -8711,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>107</v>
       </c>
@@ -8722,9 +10029,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>